--- a/data/nzd0111/nzd0111.xlsx
+++ b/data/nzd0111/nzd0111.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13270,6 +13270,126 @@
         <v>377.39</v>
       </c>
       <c r="H428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>399.77</v>
+      </c>
+      <c r="C429" t="n">
+        <v>380.41</v>
+      </c>
+      <c r="D429" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="E429" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="F429" t="n">
+        <v>374.34</v>
+      </c>
+      <c r="G429" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>399.21</v>
+      </c>
+      <c r="C430" t="n">
+        <v>379.01</v>
+      </c>
+      <c r="D430" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="E430" t="n">
+        <v>379.38</v>
+      </c>
+      <c r="F430" t="n">
+        <v>374.42</v>
+      </c>
+      <c r="G430" t="n">
+        <v>377.46</v>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>398.53</v>
+      </c>
+      <c r="C431" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="D431" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="E431" t="n">
+        <v>379.86</v>
+      </c>
+      <c r="F431" t="n">
+        <v>373.83</v>
+      </c>
+      <c r="G431" t="n">
+        <v>377.84</v>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>398.51</v>
+      </c>
+      <c r="C432" t="n">
+        <v>377.67</v>
+      </c>
+      <c r="D432" t="n">
+        <v>376.76</v>
+      </c>
+      <c r="E432" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="F432" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="G432" t="n">
+        <v>378.9</v>
+      </c>
+      <c r="H432" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13286,7 +13406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B579"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19079,6 +19199,46 @@
       </c>
       <c r="B579" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -19247,28 +19407,28 @@
         <v>0.053</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1086407139522728</v>
+        <v>0.1085075431509945</v>
       </c>
       <c r="J2" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="K2" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02119028890571162</v>
+        <v>0.02160120401496568</v>
       </c>
       <c r="M2" t="n">
-        <v>3.925271470808643</v>
+        <v>3.893116368214383</v>
       </c>
       <c r="N2" t="n">
-        <v>30.82617160946015</v>
+        <v>30.5413816639167</v>
       </c>
       <c r="O2" t="n">
-        <v>5.552132167866697</v>
+        <v>5.526425758473256</v>
       </c>
       <c r="P2" t="n">
-        <v>396.1531318280266</v>
+        <v>396.154521292751</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19325,28 +19485,28 @@
         <v>0.0517</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1365722796710327</v>
+        <v>0.1211899811771927</v>
       </c>
       <c r="J3" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="K3" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04574289124905506</v>
+        <v>0.03617231286499378</v>
       </c>
       <c r="M3" t="n">
-        <v>3.442913913373792</v>
+        <v>3.479455561154571</v>
       </c>
       <c r="N3" t="n">
-        <v>22.09990010990077</v>
+        <v>22.51335086662676</v>
       </c>
       <c r="O3" t="n">
-        <v>4.701053085203438</v>
+        <v>4.744823586459961</v>
       </c>
       <c r="P3" t="n">
-        <v>383.3393151462245</v>
+        <v>383.4981860701362</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19403,28 +19563,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1605260305361629</v>
+        <v>0.1419844502120219</v>
       </c>
       <c r="J4" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="K4" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06285795550234263</v>
+        <v>0.04901184406645653</v>
       </c>
       <c r="M4" t="n">
-        <v>3.539567437046838</v>
+        <v>3.593464620412317</v>
       </c>
       <c r="N4" t="n">
-        <v>21.82023912209207</v>
+        <v>22.50293769312857</v>
       </c>
       <c r="O4" t="n">
-        <v>4.671213881004816</v>
+        <v>4.743726140190701</v>
       </c>
       <c r="P4" t="n">
-        <v>381.9428202196164</v>
+        <v>382.1342974054943</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19481,28 +19641,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02691265158850729</v>
+        <v>0.01366905584242386</v>
       </c>
       <c r="J5" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="K5" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001980968516337778</v>
+        <v>0.0005118406552809818</v>
       </c>
       <c r="M5" t="n">
-        <v>3.527458521651966</v>
+        <v>3.553140763986821</v>
       </c>
       <c r="N5" t="n">
-        <v>20.72514742535674</v>
+        <v>20.9895677386427</v>
       </c>
       <c r="O5" t="n">
-        <v>4.552488047799438</v>
+        <v>4.581437300525098</v>
       </c>
       <c r="P5" t="n">
-        <v>386.0997154601096</v>
+        <v>386.2364682022805</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19559,28 +19719,28 @@
         <v>0.0648</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03927540046860437</v>
+        <v>-0.04996987770846657</v>
       </c>
       <c r="J6" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="K6" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00329469183289588</v>
+        <v>0.005381158185480794</v>
       </c>
       <c r="M6" t="n">
-        <v>4.068240793120789</v>
+        <v>4.077362953324267</v>
       </c>
       <c r="N6" t="n">
-        <v>26.35872482224415</v>
+        <v>26.40592102747557</v>
       </c>
       <c r="O6" t="n">
-        <v>5.134074875013428</v>
+        <v>5.138669188367312</v>
       </c>
       <c r="P6" t="n">
-        <v>380.9990642397951</v>
+        <v>381.1099931749389</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19637,28 +19797,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02572909796120841</v>
+        <v>-0.03443676610438155</v>
       </c>
       <c r="J7" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="K7" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001202091274133288</v>
+        <v>0.00218538247924871</v>
       </c>
       <c r="M7" t="n">
-        <v>4.577525456013781</v>
+        <v>4.577850686928362</v>
       </c>
       <c r="N7" t="n">
-        <v>31.06851396819445</v>
+        <v>30.97925363170289</v>
       </c>
       <c r="O7" t="n">
-        <v>5.573913702973383</v>
+        <v>5.565900972143044</v>
       </c>
       <c r="P7" t="n">
-        <v>383.0358837445018</v>
+        <v>383.126189998971</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19696,7 +19856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37659,6 +37819,174 @@
         </is>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-36.04785685571432,174.56478599161625</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-36.04816599982943,174.56562832418635</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-36.04832958356501,174.5664987457584</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-36.048397768841234,174.56737899861582</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-36.04845810856943,174.5682590687655</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-36.0483824604333,174.56914188732256</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-36.047861821390775,174.56478487596362</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-36.04817842612039,174.5656256180073</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-36.048331992998996,174.5664983237181</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-36.048392551958,174.56737941672282</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-36.04845738792424,174.56825903750106</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-36.04837509757762,174.56914109108044</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-36.04786785114073,174.56478352124242</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-36.04818694700557,174.56562376234115</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-36.04833618719889,174.5664975890553</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-36.0483882345374,174.56737976274238</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-36.048462702682656,174.56825926807636</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-36.04837168552254,174.56914072209028</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-36.047868028486334,174.56478348139768</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-36.04819031985595,174.56562302780654</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-36.0483276203225,174.56649908964306</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-36.04837870023356,174.5673805268688</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-36.048457297843576,174.56825903359302</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-36.048362167684665,174.56913969280208</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0111/nzd0111.xlsx
+++ b/data/nzd0111/nzd0111.xlsx
@@ -13406,7 +13406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B583"/>
+  <dimension ref="A1:B586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19239,6 +19239,36 @@
       </c>
       <c r="B583" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0111/nzd0111.xlsx
+++ b/data/nzd0111/nzd0111.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13392,6 +13392,66 @@
       <c r="H432" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>398.51</v>
+      </c>
+      <c r="C433" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="D433" t="n">
+        <v>376.79</v>
+      </c>
+      <c r="E433" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="F433" t="n">
+        <v>374.82</v>
+      </c>
+      <c r="G433" t="n">
+        <v>379.2</v>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>399.09</v>
+      </c>
+      <c r="C434" t="n">
+        <v>379.41</v>
+      </c>
+      <c r="D434" t="n">
+        <v>378.07</v>
+      </c>
+      <c r="E434" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="F434" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="G434" t="n">
+        <v>379.54</v>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B586"/>
+  <dimension ref="A1:B588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19269,6 +19329,26 @@
       </c>
       <c r="B586" t="n">
         <v>0.48</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -19437,28 +19517,28 @@
         <v>0.053</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1085075431509945</v>
+        <v>0.1082340797180052</v>
       </c>
       <c r="J2" t="n">
+        <v>433</v>
+      </c>
+      <c r="K2" t="n">
         <v>431</v>
       </c>
-      <c r="K2" t="n">
-        <v>429</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02160120401496568</v>
+        <v>0.02172773709757936</v>
       </c>
       <c r="M2" t="n">
-        <v>3.893116368214383</v>
+        <v>3.876169160665134</v>
       </c>
       <c r="N2" t="n">
-        <v>30.5413816639167</v>
+        <v>30.40043364006026</v>
       </c>
       <c r="O2" t="n">
-        <v>5.526425758473256</v>
+        <v>5.513658825141456</v>
       </c>
       <c r="P2" t="n">
-        <v>396.154521292751</v>
+        <v>396.1573751201072</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19515,28 +19595,28 @@
         <v>0.0517</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1211899811771927</v>
+        <v>0.1137438132086786</v>
       </c>
       <c r="J3" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K3" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03617231286499378</v>
+        <v>0.03194304681741378</v>
       </c>
       <c r="M3" t="n">
-        <v>3.479455561154571</v>
+        <v>3.497125079848569</v>
       </c>
       <c r="N3" t="n">
-        <v>22.51335086662676</v>
+        <v>22.70075747464942</v>
       </c>
       <c r="O3" t="n">
-        <v>4.744823586459961</v>
+        <v>4.764531191486673</v>
       </c>
       <c r="P3" t="n">
-        <v>383.4981860701362</v>
+        <v>383.5755733506413</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19593,28 +19673,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1419844502120219</v>
+        <v>0.1340155807428201</v>
       </c>
       <c r="J4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04901184406645653</v>
+        <v>0.04374177455128903</v>
       </c>
       <c r="M4" t="n">
-        <v>3.593464620412317</v>
+        <v>3.615234968592717</v>
       </c>
       <c r="N4" t="n">
-        <v>22.50293769312857</v>
+        <v>22.73262470493212</v>
       </c>
       <c r="O4" t="n">
-        <v>4.743726140190701</v>
+        <v>4.767874233338389</v>
       </c>
       <c r="P4" t="n">
-        <v>382.1342974054943</v>
+        <v>382.2171171520259</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19671,28 +19751,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01366905584242386</v>
+        <v>0.00913878203265654</v>
       </c>
       <c r="J5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005118406552809818</v>
+        <v>0.0002302071360095193</v>
       </c>
       <c r="M5" t="n">
-        <v>3.553140763986821</v>
+        <v>3.556894626476606</v>
       </c>
       <c r="N5" t="n">
-        <v>20.9895677386427</v>
+        <v>20.99994117321192</v>
       </c>
       <c r="O5" t="n">
-        <v>4.581437300525098</v>
+        <v>4.582569276422554</v>
       </c>
       <c r="P5" t="n">
-        <v>386.2364682022805</v>
+        <v>386.2835518230978</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19749,28 +19829,28 @@
         <v>0.0648</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04996987770846657</v>
+        <v>-0.05437589757908897</v>
       </c>
       <c r="J6" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K6" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005381158185480794</v>
+        <v>0.006411447709372409</v>
       </c>
       <c r="M6" t="n">
-        <v>4.077362953324267</v>
+        <v>4.077685734713053</v>
       </c>
       <c r="N6" t="n">
-        <v>26.40592102747557</v>
+        <v>26.38457343909751</v>
       </c>
       <c r="O6" t="n">
-        <v>5.138669188367312</v>
+        <v>5.136591616928244</v>
       </c>
       <c r="P6" t="n">
-        <v>381.1099931749389</v>
+        <v>381.1559859337568</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19827,28 +19907,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03443676610438155</v>
+        <v>-0.03708557352301683</v>
       </c>
       <c r="J7" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K7" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00218538247924871</v>
+        <v>0.002558672522740113</v>
       </c>
       <c r="M7" t="n">
-        <v>4.577850686928362</v>
+        <v>4.569475778928104</v>
       </c>
       <c r="N7" t="n">
-        <v>30.97925363170289</v>
+        <v>30.87232785628329</v>
       </c>
       <c r="O7" t="n">
-        <v>5.565900972143044</v>
+        <v>5.556287236661122</v>
       </c>
       <c r="P7" t="n">
-        <v>383.126189998971</v>
+        <v>383.1538398019106</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19886,7 +19966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38017,6 +38097,90 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-36.047868028486334,174.56478348139768</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-36.04818579313571,174.5656240136293</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-36.04832735260762,174.56649913653644</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-36.04837267383395,174.56738100985424</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-36.04845378469817,174.56825888117888</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-36.048359473956964,174.56913940149414</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-36.0478628854643,174.5647846368952</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-36.04817487575155,174.56562639120136</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-36.04831593010572,174.56650113731965</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-36.04836979555353,174.56738124053385</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-36.0484494608269,174.56825869359224</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-36.04835642106556,174.5691390713452</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
